--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR11"/>
+  <dimension ref="A1:CW11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,6 +911,31 @@
           <t>Semana 19 - Cierre</t>
         </is>
       </c>
+      <c r="CS1" t="inlineStr">
+        <is>
+          <t>Semana 20 - Fecha</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>Semana 20 - Apertura</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>Semana 20 - Máximo</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>Semana 20 - Mínimo</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>Semana 20 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1241,6 +1266,23 @@
       <c r="CR2" t="n">
         <v>7000</v>
       </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT2" t="n">
+        <v>6980</v>
+      </c>
+      <c r="CU2" t="n">
+        <v>7015</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>6655</v>
+      </c>
+      <c r="CW2" t="n">
+        <v>6685</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1571,6 +1613,23 @@
       <c r="CR3" s="1" t="n">
         <v>8835</v>
       </c>
+      <c r="CS3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT3" t="n">
+        <v>8880</v>
+      </c>
+      <c r="CU3" t="n">
+        <v>9220</v>
+      </c>
+      <c r="CV3" t="n">
+        <v>8605</v>
+      </c>
+      <c r="CW3" t="n">
+        <v>8760</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1901,6 +1960,23 @@
       <c r="CR4" s="1" t="n">
         <v>5525</v>
       </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT4" t="n">
+        <v>5505</v>
+      </c>
+      <c r="CU4" t="n">
+        <v>5640</v>
+      </c>
+      <c r="CV4" t="n">
+        <v>5190</v>
+      </c>
+      <c r="CW4" t="n">
+        <v>5215</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2231,6 +2307,23 @@
       <c r="CR5" t="n">
         <v>12420</v>
       </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT5" t="n">
+        <v>12400</v>
+      </c>
+      <c r="CU5" t="n">
+        <v>12600</v>
+      </c>
+      <c r="CV5" t="n">
+        <v>11870</v>
+      </c>
+      <c r="CW5" t="n">
+        <v>12060</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2561,6 +2654,23 @@
       <c r="CR6" t="n">
         <v>668</v>
       </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT6" t="n">
+        <v>670</v>
+      </c>
+      <c r="CU6" t="n">
+        <v>680</v>
+      </c>
+      <c r="CV6" t="n">
+        <v>648</v>
+      </c>
+      <c r="CW6" t="n">
+        <v>662</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2891,6 +3001,23 @@
       <c r="CR7" s="1" t="n">
         <v>871.5</v>
       </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT7" t="n">
+        <v>874.5</v>
+      </c>
+      <c r="CU7" t="n">
+        <v>889</v>
+      </c>
+      <c r="CV7" t="n">
+        <v>840</v>
+      </c>
+      <c r="CW7" t="n">
+        <v>856.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3221,6 +3348,23 @@
       <c r="CR8" s="1" t="n">
         <v>2253</v>
       </c>
+      <c r="CS8" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT8" t="n">
+        <v>2240</v>
+      </c>
+      <c r="CU8" t="n">
+        <v>2313</v>
+      </c>
+      <c r="CV8" t="n">
+        <v>2055</v>
+      </c>
+      <c r="CW8" t="n">
+        <v>2078</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3551,6 +3695,23 @@
       <c r="CR9" s="1" t="n">
         <v>1954</v>
       </c>
+      <c r="CS9" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT9" t="n">
+        <v>1950</v>
+      </c>
+      <c r="CU9" t="n">
+        <v>1970</v>
+      </c>
+      <c r="CV9" t="n">
+        <v>1870</v>
+      </c>
+      <c r="CW9" t="n">
+        <v>1881</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3881,6 +4042,23 @@
       <c r="CR10" t="n">
         <v>3120</v>
       </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT10" t="n">
+        <v>3120</v>
+      </c>
+      <c r="CU10" t="n">
+        <v>3140</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>2992.5</v>
+      </c>
+      <c r="CW10" t="n">
+        <v>3045</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4210,6 +4388,23 @@
       </c>
       <c r="CR11" s="1" t="n">
         <v>9515</v>
+      </c>
+      <c r="CS11" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="CT11" t="n">
+        <v>9490</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>9650</v>
+      </c>
+      <c r="CV11" t="n">
+        <v>9035</v>
+      </c>
+      <c r="CW11" t="n">
+        <v>9055</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CW11"/>
+  <dimension ref="A1:DB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -936,6 +936,31 @@
           <t>Semana 20 - Cierre</t>
         </is>
       </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>Semana 21 - Fecha</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>Semana 21 - Apertura</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>Semana 21 - Máximo</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>Semana 21 - Mínimo</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>Semana 21 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1283,6 +1308,23 @@
       <c r="CW2" t="n">
         <v>6685</v>
       </c>
+      <c r="CX2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY2" t="n">
+        <v>6670</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>6755</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>6270</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>6290</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1630,6 +1672,23 @@
       <c r="CW3" t="n">
         <v>8760</v>
       </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY3" t="n">
+        <v>8760</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>8910</v>
+      </c>
+      <c r="DA3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="DB3" t="n">
+        <v>8440</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1977,6 +2036,23 @@
       <c r="CW4" t="n">
         <v>5215</v>
       </c>
+      <c r="CX4" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY4" t="n">
+        <v>5170</v>
+      </c>
+      <c r="CZ4" t="n">
+        <v>5250</v>
+      </c>
+      <c r="DA4" t="n">
+        <v>5010</v>
+      </c>
+      <c r="DB4" t="n">
+        <v>5060</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2324,6 +2400,23 @@
       <c r="CW5" t="n">
         <v>12060</v>
       </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY5" t="n">
+        <v>12070</v>
+      </c>
+      <c r="CZ5" t="n">
+        <v>12200</v>
+      </c>
+      <c r="DA5" t="n">
+        <v>11090</v>
+      </c>
+      <c r="DB5" t="n">
+        <v>11110</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2671,6 +2764,23 @@
       <c r="CW6" t="n">
         <v>662</v>
       </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY6" t="n">
+        <v>661.5</v>
+      </c>
+      <c r="CZ6" t="n">
+        <v>673</v>
+      </c>
+      <c r="DA6" t="n">
+        <v>645</v>
+      </c>
+      <c r="DB6" t="n">
+        <v>657</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3018,6 +3128,23 @@
       <c r="CW7" t="n">
         <v>856.5</v>
       </c>
+      <c r="CX7" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY7" t="n">
+        <v>857.5</v>
+      </c>
+      <c r="CZ7" t="n">
+        <v>867.5</v>
+      </c>
+      <c r="DA7" t="n">
+        <v>833</v>
+      </c>
+      <c r="DB7" t="n">
+        <v>844</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3365,6 +3492,23 @@
       <c r="CW8" t="n">
         <v>2078</v>
       </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY8" t="n">
+        <v>2120</v>
+      </c>
+      <c r="CZ8" t="n">
+        <v>2120</v>
+      </c>
+      <c r="DA8" t="n">
+        <v>1971</v>
+      </c>
+      <c r="DB8" t="n">
+        <v>2021</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3712,6 +3856,23 @@
       <c r="CW9" t="n">
         <v>1881</v>
       </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="CZ9" t="n">
+        <v>1904</v>
+      </c>
+      <c r="DA9" t="n">
+        <v>1730</v>
+      </c>
+      <c r="DB9" t="n">
+        <v>1736</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4059,6 +4220,23 @@
       <c r="CW10" t="n">
         <v>3045</v>
       </c>
+      <c r="CX10" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY10" t="n">
+        <v>3132.5</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>3132.5</v>
+      </c>
+      <c r="DA10" t="n">
+        <v>2990</v>
+      </c>
+      <c r="DB10" t="n">
+        <v>3012.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4405,6 +4583,23 @@
       </c>
       <c r="CW11" t="n">
         <v>9055</v>
+      </c>
+      <c r="CX11" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="CY11" t="n">
+        <v>9000</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>9100</v>
+      </c>
+      <c r="DA11" t="n">
+        <v>8550</v>
+      </c>
+      <c r="DB11" t="n">
+        <v>8640</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DB11"/>
+  <dimension ref="A1:DG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -961,6 +961,31 @@
           <t>Semana 21 - Cierre</t>
         </is>
       </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>Semana 22 - Fecha</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>Semana 22 - Apertura</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>Semana 22 - Máximo</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>Semana 22 - Mínimo</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>Semana 22 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1325,6 +1350,23 @@
       <c r="DB2" t="n">
         <v>6290</v>
       </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD2" t="n">
+        <v>6250</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>6250</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>5710</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>5835</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1689,6 +1731,23 @@
       <c r="DB3" t="n">
         <v>8440</v>
       </c>
+      <c r="DC3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD3" t="n">
+        <v>8490</v>
+      </c>
+      <c r="DE3" t="n">
+        <v>8600</v>
+      </c>
+      <c r="DF3" t="n">
+        <v>7875</v>
+      </c>
+      <c r="DG3" t="n">
+        <v>8050</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2053,6 +2112,23 @@
       <c r="DB4" t="n">
         <v>5060</v>
       </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD4" t="n">
+        <v>5075</v>
+      </c>
+      <c r="DE4" t="n">
+        <v>5130</v>
+      </c>
+      <c r="DF4" t="n">
+        <v>4860</v>
+      </c>
+      <c r="DG4" t="n">
+        <v>4972.5</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2417,6 +2493,23 @@
       <c r="DB5" t="n">
         <v>11110</v>
       </c>
+      <c r="DC5" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD5" t="n">
+        <v>10940</v>
+      </c>
+      <c r="DE5" t="n">
+        <v>11090</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>10250</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>10500</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2781,6 +2874,23 @@
       <c r="DB6" t="n">
         <v>657</v>
       </c>
+      <c r="DC6" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD6" t="n">
+        <v>657</v>
+      </c>
+      <c r="DE6" t="n">
+        <v>678</v>
+      </c>
+      <c r="DF6" s="2" t="n">
+        <v>625</v>
+      </c>
+      <c r="DG6" s="1" t="n">
+        <v>674.5</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3145,6 +3255,23 @@
       <c r="DB7" t="n">
         <v>844</v>
       </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD7" t="n">
+        <v>849.5</v>
+      </c>
+      <c r="DE7" t="n">
+        <v>849.5</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>792</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>817</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3509,6 +3636,23 @@
       <c r="DB8" t="n">
         <v>2021</v>
       </c>
+      <c r="DC8" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD8" t="n">
+        <v>2000</v>
+      </c>
+      <c r="DE8" t="n">
+        <v>2060</v>
+      </c>
+      <c r="DF8" t="n">
+        <v>1883</v>
+      </c>
+      <c r="DG8" t="n">
+        <v>1893</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3873,6 +4017,23 @@
       <c r="DB9" t="n">
         <v>1736</v>
       </c>
+      <c r="DC9" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD9" t="n">
+        <v>1748</v>
+      </c>
+      <c r="DE9" t="n">
+        <v>1748</v>
+      </c>
+      <c r="DF9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DG9" t="n">
+        <v>1616</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4237,6 +4398,23 @@
       <c r="DB10" t="n">
         <v>3012.5</v>
       </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD10" t="n">
+        <v>3012.5</v>
+      </c>
+      <c r="DE10" t="n">
+        <v>3040</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>2837.5</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>2980</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4600,6 +4778,23 @@
       </c>
       <c r="DB11" t="n">
         <v>8640</v>
+      </c>
+      <c r="DC11" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="DD11" t="n">
+        <v>8610</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>8795</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>8010</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>8105</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DG11"/>
+  <dimension ref="A1:DL11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -986,6 +986,31 @@
           <t>Semana 22 - Cierre</t>
         </is>
       </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>Semana 23 - Fecha</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>Semana 23 - Apertura</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>Semana 23 - Máximo</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>Semana 23 - Mínimo</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>Semana 23 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1367,6 +1392,23 @@
       <c r="DG2" t="n">
         <v>5835</v>
       </c>
+      <c r="DH2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI2" t="n">
+        <v>5975</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>6230</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>5885</v>
+      </c>
+      <c r="DL2" s="1" t="n">
+        <v>5940</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1748,6 +1790,23 @@
       <c r="DG3" t="n">
         <v>8050</v>
       </c>
+      <c r="DH3" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI3" t="n">
+        <v>8155</v>
+      </c>
+      <c r="DJ3" t="n">
+        <v>8320</v>
+      </c>
+      <c r="DK3" t="n">
+        <v>7940</v>
+      </c>
+      <c r="DL3" s="1" t="n">
+        <v>8065</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2129,6 +2188,23 @@
       <c r="DG4" t="n">
         <v>4972.5</v>
       </c>
+      <c r="DH4" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI4" t="n">
+        <v>4982.5</v>
+      </c>
+      <c r="DJ4" t="n">
+        <v>5340</v>
+      </c>
+      <c r="DK4" t="n">
+        <v>4980</v>
+      </c>
+      <c r="DL4" s="1" t="n">
+        <v>5190</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2510,6 +2586,23 @@
       <c r="DG5" t="n">
         <v>10500</v>
       </c>
+      <c r="DH5" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI5" t="n">
+        <v>10600</v>
+      </c>
+      <c r="DJ5" t="n">
+        <v>11190</v>
+      </c>
+      <c r="DK5" t="n">
+        <v>10390</v>
+      </c>
+      <c r="DL5" t="n">
+        <v>10440</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2891,6 +2984,23 @@
       <c r="DG6" s="1" t="n">
         <v>674.5</v>
       </c>
+      <c r="DH6" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI6" t="n">
+        <v>651</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>687.5</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>650</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>671</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3272,6 +3382,23 @@
       <c r="DG7" t="n">
         <v>817</v>
       </c>
+      <c r="DH7" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI7" t="n">
+        <v>820</v>
+      </c>
+      <c r="DJ7" t="n">
+        <v>842</v>
+      </c>
+      <c r="DK7" t="n">
+        <v>800</v>
+      </c>
+      <c r="DL7" s="1" t="n">
+        <v>839.5</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3653,6 +3780,23 @@
       <c r="DG8" t="n">
         <v>1893</v>
       </c>
+      <c r="DH8" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI8" t="n">
+        <v>1960</v>
+      </c>
+      <c r="DJ8" t="n">
+        <v>2093</v>
+      </c>
+      <c r="DK8" t="n">
+        <v>1911</v>
+      </c>
+      <c r="DL8" s="1" t="n">
+        <v>2034</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4034,6 +4178,23 @@
       <c r="DG9" t="n">
         <v>1616</v>
       </c>
+      <c r="DH9" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI9" t="n">
+        <v>1650</v>
+      </c>
+      <c r="DJ9" t="n">
+        <v>1770</v>
+      </c>
+      <c r="DK9" t="n">
+        <v>1600</v>
+      </c>
+      <c r="DL9" s="1" t="n">
+        <v>1627</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4415,6 +4576,23 @@
       <c r="DG10" t="n">
         <v>2980</v>
       </c>
+      <c r="DH10" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI10" t="n">
+        <v>2980</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>3280</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>2960</v>
+      </c>
+      <c r="DL10" s="1" t="n">
+        <v>3257.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4795,6 +4973,23 @@
       </c>
       <c r="DG11" t="n">
         <v>8105</v>
+      </c>
+      <c r="DH11" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="DI11" t="n">
+        <v>8150</v>
+      </c>
+      <c r="DJ11" t="n">
+        <v>8810</v>
+      </c>
+      <c r="DK11" t="n">
+        <v>8150</v>
+      </c>
+      <c r="DL11" s="1" t="n">
+        <v>8340</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DL11"/>
+  <dimension ref="A1:DQ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1011,6 +1011,31 @@
           <t>Semana 23 - Cierre</t>
         </is>
       </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>Semana 24 - Fecha</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>Semana 24 - Apertura</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>Semana 24 - Máximo</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>Semana 24 - Mínimo</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>Semana 24 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1409,6 +1434,23 @@
       <c r="DL2" s="1" t="n">
         <v>5940</v>
       </c>
+      <c r="DM2" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN2" t="n">
+        <v>5940</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>6070</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>5620</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>5805</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1807,6 +1849,23 @@
       <c r="DL3" s="1" t="n">
         <v>8065</v>
       </c>
+      <c r="DM3" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN3" t="n">
+        <v>8065</v>
+      </c>
+      <c r="DO3" t="n">
+        <v>8560</v>
+      </c>
+      <c r="DP3" t="n">
+        <v>8065</v>
+      </c>
+      <c r="DQ3" s="1" t="n">
+        <v>8430</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2205,6 +2264,23 @@
       <c r="DL4" s="1" t="n">
         <v>5190</v>
       </c>
+      <c r="DM4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN4" t="n">
+        <v>5190</v>
+      </c>
+      <c r="DO4" t="n">
+        <v>5295</v>
+      </c>
+      <c r="DP4" t="n">
+        <v>5140</v>
+      </c>
+      <c r="DQ4" s="1" t="n">
+        <v>5240</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2603,6 +2679,23 @@
       <c r="DL5" t="n">
         <v>10440</v>
       </c>
+      <c r="DM5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN5" t="n">
+        <v>10440</v>
+      </c>
+      <c r="DO5" t="n">
+        <v>10750</v>
+      </c>
+      <c r="DP5" t="n">
+        <v>10100</v>
+      </c>
+      <c r="DQ5" t="n">
+        <v>10340</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3001,6 +3094,23 @@
       <c r="DL6" t="n">
         <v>671</v>
       </c>
+      <c r="DM6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN6" t="n">
+        <v>671</v>
+      </c>
+      <c r="DO6" t="n">
+        <v>729</v>
+      </c>
+      <c r="DP6" t="n">
+        <v>663</v>
+      </c>
+      <c r="DQ6" s="1" t="n">
+        <v>709</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3399,6 +3509,23 @@
       <c r="DL7" s="1" t="n">
         <v>839.5</v>
       </c>
+      <c r="DM7" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN7" t="n">
+        <v>839.5</v>
+      </c>
+      <c r="DO7" t="n">
+        <v>852</v>
+      </c>
+      <c r="DP7" t="n">
+        <v>822</v>
+      </c>
+      <c r="DQ7" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3797,6 +3924,23 @@
       <c r="DL8" s="1" t="n">
         <v>2034</v>
       </c>
+      <c r="DM8" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN8" t="n">
+        <v>2034</v>
+      </c>
+      <c r="DO8" t="n">
+        <v>2143</v>
+      </c>
+      <c r="DP8" t="n">
+        <v>2029</v>
+      </c>
+      <c r="DQ8" s="1" t="n">
+        <v>2078</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4195,6 +4339,23 @@
       <c r="DL9" s="1" t="n">
         <v>1627</v>
       </c>
+      <c r="DM9" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN9" t="n">
+        <v>1627</v>
+      </c>
+      <c r="DO9" t="n">
+        <v>1698</v>
+      </c>
+      <c r="DP9" t="n">
+        <v>1627</v>
+      </c>
+      <c r="DQ9" s="1" t="n">
+        <v>1660</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4593,6 +4754,23 @@
       <c r="DL10" s="1" t="n">
         <v>3257.5</v>
       </c>
+      <c r="DM10" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN10" t="n">
+        <v>3257.5</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>3300</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>3100</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>3257.5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -4990,6 +5168,23 @@
       </c>
       <c r="DL11" s="1" t="n">
         <v>8340</v>
+      </c>
+      <c r="DM11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="DN11" t="n">
+        <v>8340</v>
+      </c>
+      <c r="DO11" t="n">
+        <v>8565</v>
+      </c>
+      <c r="DP11" t="n">
+        <v>8180</v>
+      </c>
+      <c r="DQ11" s="1" t="n">
+        <v>8445</v>
       </c>
     </row>
   </sheetData>

--- a/registro_merval.xlsx
+++ b/registro_merval.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:DQ11"/>
+  <dimension ref="A1:DV11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,31 @@
           <t>Semana 24 - Cierre</t>
         </is>
       </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>Semana 25 - Fecha</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>Semana 25 - Apertura</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>Semana 25 - Máximo</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>Semana 25 - Mínimo</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>Semana 25 - Cierre</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1451,6 +1476,23 @@
       <c r="DQ2" t="n">
         <v>5805</v>
       </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS2" t="n">
+        <v>5850</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>6275</v>
+      </c>
+      <c r="DU2" s="2" t="n">
+        <v>5610</v>
+      </c>
+      <c r="DV2" s="1" t="n">
+        <v>6260</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1866,6 +1908,23 @@
       <c r="DQ3" s="1" t="n">
         <v>8430</v>
       </c>
+      <c r="DR3" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS3" t="n">
+        <v>8430</v>
+      </c>
+      <c r="DT3" t="n">
+        <v>8440</v>
+      </c>
+      <c r="DU3" t="n">
+        <v>7905</v>
+      </c>
+      <c r="DV3" t="n">
+        <v>8350</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2281,6 +2340,23 @@
       <c r="DQ4" s="1" t="n">
         <v>5240</v>
       </c>
+      <c r="DR4" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS4" t="n">
+        <v>5240</v>
+      </c>
+      <c r="DT4" t="n">
+        <v>5300</v>
+      </c>
+      <c r="DU4" s="2" t="n">
+        <v>4982.5</v>
+      </c>
+      <c r="DV4" s="1" t="n">
+        <v>5250</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2696,6 +2772,23 @@
       <c r="DQ5" t="n">
         <v>10340</v>
       </c>
+      <c r="DR5" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS5" t="n">
+        <v>10350</v>
+      </c>
+      <c r="DT5" t="n">
+        <v>10940</v>
+      </c>
+      <c r="DU5" s="2" t="n">
+        <v>10050</v>
+      </c>
+      <c r="DV5" s="1" t="n">
+        <v>10870</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3111,6 +3204,23 @@
       <c r="DQ6" s="1" t="n">
         <v>709</v>
       </c>
+      <c r="DR6" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS6" t="n">
+        <v>709</v>
+      </c>
+      <c r="DT6" t="n">
+        <v>788</v>
+      </c>
+      <c r="DU6" t="n">
+        <v>685</v>
+      </c>
+      <c r="DV6" s="1" t="n">
+        <v>776</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3526,6 +3636,23 @@
       <c r="DQ7" t="n">
         <v>833</v>
       </c>
+      <c r="DR7" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS7" t="n">
+        <v>855</v>
+      </c>
+      <c r="DT7" t="n">
+        <v>897.5</v>
+      </c>
+      <c r="DU7" s="2" t="n">
+        <v>802</v>
+      </c>
+      <c r="DV7" s="1" t="n">
+        <v>887</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3941,6 +4068,23 @@
       <c r="DQ8" s="1" t="n">
         <v>2078</v>
       </c>
+      <c r="DR8" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS8" t="n">
+        <v>2040</v>
+      </c>
+      <c r="DT8" t="n">
+        <v>2106</v>
+      </c>
+      <c r="DU8" t="n">
+        <v>1915</v>
+      </c>
+      <c r="DV8" t="n">
+        <v>1992</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -4356,6 +4500,23 @@
       <c r="DQ9" s="1" t="n">
         <v>1660</v>
       </c>
+      <c r="DR9" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS9" t="n">
+        <v>1645</v>
+      </c>
+      <c r="DT9" t="n">
+        <v>1669</v>
+      </c>
+      <c r="DU9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="DV9" t="n">
+        <v>1564</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -4771,6 +4932,23 @@
       <c r="DQ10" t="n">
         <v>3257.5</v>
       </c>
+      <c r="DR10" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS10" t="n">
+        <v>3257.5</v>
+      </c>
+      <c r="DT10" t="n">
+        <v>3280</v>
+      </c>
+      <c r="DU10" t="n">
+        <v>3047.5</v>
+      </c>
+      <c r="DV10" t="n">
+        <v>3220</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5185,6 +5363,23 @@
       </c>
       <c r="DQ11" s="1" t="n">
         <v>8445</v>
+      </c>
+      <c r="DR11" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="DS11" t="n">
+        <v>8445</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>9010</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>8235</v>
+      </c>
+      <c r="DV11" s="1" t="n">
+        <v>8985</v>
       </c>
     </row>
   </sheetData>
